--- a/outputs/evaluation/architecture/validation/CF_M09/run_3/CF_M09_arch_eval.xlsx
+++ b/outputs/evaluation/architecture/validation/CF_M09/run_3/CF_M09_arch_eval.xlsx
@@ -451,10 +451,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7917</v>
+        <v>0.7692</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4043</v>
+        <v>0.4167</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -469,13 +469,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.85</v>
+        <v>0.8636</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4048</v>
+        <v>0.4419</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9667</v>
+        <v>0.9578</v>
       </c>
     </row>
     <row r="4">
@@ -485,13 +485,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="C4" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8038999999999999</v>
+        <v>0.7516</v>
       </c>
     </row>
     <row r="7">
@@ -518,7 +518,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7368</v>
+        <v>0.8</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -533,10 +533,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.5881999999999999</v>
+        <v>0.6842</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8058</v>
+        <v>0.8142</v>
       </c>
     </row>
     <row r="10">
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6316000000000001</v>
+        <v>0.75</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1818</v>
+        <v>0.2</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -639,19 +639,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D2" t="n">
         <v>13</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8125</v>
+        <v>0.8667</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3824</v>
+        <v>0.3714</v>
       </c>
     </row>
     <row r="3">
@@ -664,16 +664,16 @@
         <v>8</v>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>0.8571</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="4">
@@ -689,13 +689,13 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
     </row>
   </sheetData>
@@ -731,7 +731,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3">
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4">
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5">
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6">
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7917</v>
+        <v>0.7692</v>
       </c>
     </row>
     <row r="9">
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.4043</v>
+        <v>0.4167</v>
       </c>
     </row>
     <row r="10">
@@ -877,25 +877,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C2" t="n">
+        <v>22</v>
+      </c>
+      <c r="D2" t="n">
+        <v>19</v>
+      </c>
+      <c r="E2" t="n">
+        <v>19</v>
+      </c>
+      <c r="F2" t="n">
+        <v>19</v>
+      </c>
+      <c r="G2" t="n">
+        <v>19</v>
+      </c>
+      <c r="H2" t="n">
         <v>20</v>
-      </c>
-      <c r="D2" t="n">
-        <v>17</v>
-      </c>
-      <c r="E2" t="n">
-        <v>17</v>
-      </c>
-      <c r="F2" t="n">
-        <v>17</v>
-      </c>
-      <c r="G2" t="n">
-        <v>17</v>
-      </c>
-      <c r="H2" t="n">
-        <v>19</v>
       </c>
     </row>
     <row r="3">
@@ -911,19 +911,19 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4">
@@ -933,25 +933,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C4" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5">
@@ -961,25 +961,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C5" t="n">
+        <v>22</v>
+      </c>
+      <c r="D5" t="n">
+        <v>19</v>
+      </c>
+      <c r="E5" t="n">
+        <v>19</v>
+      </c>
+      <c r="F5" t="n">
+        <v>19</v>
+      </c>
+      <c r="G5" t="n">
+        <v>13</v>
+      </c>
+      <c r="H5" t="n">
         <v>20</v>
-      </c>
-      <c r="D5" t="n">
-        <v>17</v>
-      </c>
-      <c r="E5" t="n">
-        <v>17</v>
-      </c>
-      <c r="F5" t="n">
-        <v>17</v>
-      </c>
-      <c r="G5" t="n">
-        <v>10</v>
-      </c>
-      <c r="H5" t="n">
-        <v>19</v>
       </c>
     </row>
     <row r="6">
@@ -989,25 +989,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C6" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G6" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7">
@@ -1020,22 +1020,22 @@
         <v>41</v>
       </c>
       <c r="C7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D7" t="n">
         <v>16</v>
       </c>
       <c r="E7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G7" t="n">
         <v>2</v>
       </c>
       <c r="H7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8">
@@ -1063,7 +1063,7 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -1077,7 +1077,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T20"/>
+  <dimension ref="A1:T21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1185,7 +1185,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AU_15</t>
+          <t>AU_17</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>57,58</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -1225,7 +1225,7 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>AU_15</t>
+          <t>AU_17</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Service responsible for user management, authentication and authorization.</t>
+          <t>Service responsible for user management, authentication and authorization, and processing requests.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>The observer pattern is a software design pattern that defines a one-to-many dependency between objects, so that when one object changes its state, all objects that depend on it are notified and updated automatically.</t>
+          <t>The observer pattern defines a one-to-many dependency between objects, so that when one object changes its state, all objects that depend on it are notified and updated automatically.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1427,94 +1427,90 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AU_14</t>
+          <t>P_05</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CF_M09_AU07</t>
+          <t>CF_M09_P05</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>connector</t>
+          <t>pattern</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.8562</v>
-      </c>
-      <c r="E5" t="inlineStr"/>
+        <v>0.8811</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Provider</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Design Pattern</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Por un lado est´ a el cliente, quien realiza las diferentes peticiones, y por otro lado est´ a el servidor, quien las recibe y las procesa. [...] La comunicaci´ on entre ambos se realiza a trav´ es de internet utilizando el modelo de REST API y el protocolo de comunicaci´ on HTTP.</t>
+          <t>The provider pattern allows sharing information between React components without using props.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>['AU_01', 'AU_02']</t>
-        </is>
-      </c>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>AU_14</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>client, server</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>P_05</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Provider pattern</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Design Pattern</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>On one side is the client, who makes the various requests, and on the other side is the server, who receives and processes them.</t>
+          <t>The provider pattern is a software design pattern that allows sharing information between React components without the need to use props.</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>CF_M09_AU06, CF_M09_AU05</t>
+          <t>CF_M09_AU01</t>
         </is>
       </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
-          <t>CF_M09_AU07</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>client, waapiti platform</t>
-        </is>
-      </c>
+          <t>CF_M09_P05</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P_01</t>
+          <t>P_07</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CF_M09_P01</t>
+          <t>CF_M09_P07</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1523,59 +1519,63 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.9061</v>
+        <v>0.8833</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Client-Server</t>
+          <t>Hook</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Architectural Pattern</t>
+          <t>Design Pattern</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>The platform is a web service that follows the client-server architecture, where the client makes requests to a server that processes them and returns the response.</t>
+          <t>Hooks are functions that allow hooking into React state and other features.</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>59</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>P_01</t>
+          <t>P_07</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Client-Server Architecture</t>
+          <t>Hook pattern</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Architectural Pattern</t>
+          <t>Design Pattern</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>The Waapiti platform is a web service, therefore, as is usual in this type of software, it follows the client-server architecture.</t>
+          <t>Hooks are a new feature in React that allows you to use state and other React features without writing a class.</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>55</v>
-      </c>
-      <c r="Q6" t="inlineStr"/>
+        <v>59</v>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>CF_M09_AU01</t>
+        </is>
+      </c>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
-          <t>CF_M09_P01</t>
+          <t>CF_M09_P07</t>
         </is>
       </c>
       <c r="T6" t="inlineStr"/>
@@ -1583,35 +1583,35 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AU_04</t>
+          <t>P_01</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CF_M09_AU19</t>
+          <t>CF_M09_P01</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>pattern</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.9173</v>
+        <v>0.9061</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Business Layer</t>
+          <t>Client-Server</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Layer</t>
+          <t>Architectural Pattern</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>It is the layer that is responsible for processing the information.</t>
+          <t>The platform is a web service that follows the client-server architecture.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1623,37 +1623,33 @@
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>AU_04</t>
+          <t>P_01</t>
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Business layer (Backend)</t>
+          <t>Client-Server Architecture</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Layer</t>
+          <t>Architectural Pattern</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t xml:space="preserve">The business layer is divided into two services hosted on different machines. </t>
+          <t>The Waapiti platform is a web service, therefore, as is usual in this type of software, it follows the client-server architecture.</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>57</v>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>CF_M09_P02</t>
-        </is>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
-          <t>CF_M09_AU19</t>
+          <t>CF_M09_P01</t>
         </is>
       </c>
       <c r="T7" t="inlineStr"/>
@@ -1661,12 +1657,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AU_03</t>
+          <t>AU_04</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CF_M09_AU08</t>
+          <t>CF_M09_AU19</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1675,11 +1671,11 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.989</v>
+        <v>0.9173</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Presentation Layer</t>
+          <t>Business Layer</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1689,7 +1685,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>It is the layer that is responsible for displaying information to the user.</t>
+          <t>It is the layer that is responsible for processing the information, which is the server.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1701,13 +1697,13 @@
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>AU_03</t>
+          <t>AU_04</t>
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Presentation layer</t>
+          <t>Business layer (Backend)</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1717,11 +1713,11 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>This layer is responsible for displaying information to the user.</t>
+          <t xml:space="preserve">The business layer is divided into two services hosted on different machines. </t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1731,7 +1727,7 @@
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
-          <t>CF_M09_AU08</t>
+          <t>CF_M09_AU19</t>
         </is>
       </c>
       <c r="T8" t="inlineStr"/>
@@ -1739,12 +1735,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AU_05</t>
+          <t>AU_03</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CF_M09_AU10</t>
+          <t>CF_M09_AU08</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1753,11 +1749,11 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.9923</v>
+        <v>0.989</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Layer</t>
+          <t>Presentation Layer</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1767,7 +1763,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>It is the layer that is responsible for storing the information.</t>
+          <t>It is the layer that is responsible for displaying information to the user, which is the web browser.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1779,13 +1775,13 @@
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>AU_05</t>
+          <t>AU_03</t>
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Data layer</t>
+          <t>Presentation layer</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1795,7 +1791,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>This is the layer responsible for storing information.</t>
+          <t>This layer is responsible for displaying information to the user.</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -1809,7 +1805,7 @@
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
-          <t>CF_M09_AU10</t>
+          <t>CF_M09_AU08</t>
         </is>
       </c>
       <c r="T9" t="inlineStr"/>
@@ -1817,12 +1813,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AU_08</t>
+          <t>AU_05</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CF_M09_AU01</t>
+          <t>CF_M09_AU10</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1831,67 +1827,63 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>0.9923</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>React</t>
+          <t>Data Layer</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Layer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>JavaScript library used for building user interfaces in the frontend.</t>
+          <t>It is the layer that is responsible for storing all the data.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>['AU_03']</t>
-        </is>
-      </c>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>AU_08</t>
+          <t>AU_05</t>
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>React</t>
+          <t>Data layer</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Layer</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Within the software engineering specialization, this project focuses on web technologies, specifically using React [2] and Nest [3] for the codebase and AWS cloud services [4] for the infrastructure.</t>
+          <t>This is the layer responsible for storing information.</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>9</v>
+        <v>55</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>CF_M09_AU34</t>
+          <t>CF_M09_P02</t>
         </is>
       </c>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
-          <t>CF_M09_AU01</t>
+          <t>CF_M09_AU10</t>
         </is>
       </c>
       <c r="T10" t="inlineStr"/>
@@ -1899,12 +1891,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AU_11</t>
+          <t>AU_08</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CF_M09_AU24</t>
+          <t>CF_M09_AU01</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1917,7 +1909,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MySQL</t>
+          <t>React</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1927,29 +1919,29 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Relational database used to store system information.</t>
+          <t>JavaScript library used for building user interfaces in the frontend.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>60</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>['AU_05']</t>
+          <t>['AU_03']</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>AU_11</t>
+          <t>AU_08</t>
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>MySQL</t>
+          <t>React</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1959,21 +1951,21 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>RDS is a distributed relational database service. In the case of Waapiti, a MySQL database is used and contains all the system information.</t>
+          <t>Within the software engineering specialization, this project focuses on web technologies, specifically using React [2] and Nest [3] for the codebase and AWS cloud services [4] for the infrastructure.</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>58</v>
+        <v>9</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>CF_M09_AU23</t>
+          <t>CF_M09_AU34</t>
         </is>
       </c>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
-          <t>CF_M09_AU24</t>
+          <t>CF_M09_AU01</t>
         </is>
       </c>
       <c r="T11" t="inlineStr"/>
@@ -1981,12 +1973,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AU_18</t>
+          <t>AU_11</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CF_M09_AU22</t>
+          <t>CF_M09_AU24</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1999,7 +1991,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>REST</t>
+          <t>MySQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2009,29 +2001,29 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>La comunicaci´ on entre ambos se realiza a trav´ es de internet utilizando el modelo de REST API y el protocolo de comunicaci´ on HTTP.</t>
+          <t>Relational database management system used for storing system information.</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>58</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>['AU_14']</t>
+          <t>['AU_05']</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>AU_18</t>
+          <t>AU_11</t>
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>REST</t>
+          <t>MySQL</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -2041,7 +2033,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Defines REST API routes and processes requests to send them to the functional service.</t>
+          <t>RDS is a distributed relational database service. In the case of Waapiti, a MySQL database is used and contains all the system information.</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -2049,13 +2041,13 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>CF_M09_AU20</t>
+          <t>CF_M09_AU23</t>
         </is>
       </c>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
-          <t>CF_M09_AU22</t>
+          <t>CF_M09_AU24</t>
         </is>
       </c>
       <c r="T12" t="inlineStr"/>
@@ -2063,12 +2055,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AU_09</t>
+          <t>AU_14</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CF_M09_AU02</t>
+          <t>CF_M09_AU40</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2081,7 +2073,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>NestJS</t>
+          <t>HTTP</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2091,29 +2083,29 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Framework used to create the backend API.</t>
+          <t>Communication protocol used between client and server.</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>55</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>['AU_06', 'AU_07']</t>
+          <t>['AU_16']</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>AU_09</t>
+          <t>AU_14</t>
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>NestJS</t>
+          <t>HTTP</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2123,21 +2115,17 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Within the software engineering specialization, this project focuses on web technologies, specifically using React [2] and Nest [3] for the codebase and AWS cloud services [4] for the infrastructure.</t>
+          <t xml:space="preserve">Communication between the two is carried out via the internet using the REST API model [30] and the HTTP communication protocol </t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>CF_M09_AU33</t>
-        </is>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
-          <t>CF_M09_AU02</t>
+          <t>CF_M09_AU40</t>
         </is>
       </c>
       <c r="T13" t="inlineStr"/>
@@ -2145,12 +2133,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AU_01</t>
+          <t>AU_09</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CF_M09_AU06</t>
+          <t>CF_M09_AU02</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2163,59 +2151,63 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Client</t>
+          <t>NestJS</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>The client is the user of the platform.</t>
+          <t>NodeJS framework used to create backend applications.</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>['AU_06', 'AU_07']</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>AU_01</t>
+          <t>AU_09</t>
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Client</t>
+          <t>NestJS</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>On one side is the client, who makes the various requests, and on the other side is the server, who receives and processes them.</t>
+          <t>Within the software engineering specialization, this project focuses on web technologies, specifically using React [2] and Nest [3] for the codebase and AWS cloud services [4] for the infrastructure.</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>55</v>
+        <v>9</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>CF_M09_P01</t>
+          <t>CF_M09_AU33</t>
         </is>
       </c>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
-          <t>CF_M09_AU06</t>
+          <t>CF_M09_AU02</t>
         </is>
       </c>
       <c r="T14" t="inlineStr"/>
@@ -2223,12 +2215,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AU_12</t>
+          <t>AU_01</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CF_M09_AU25</t>
+          <t>CF_M09_AU06</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2241,63 +2233,59 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Amazon S3</t>
+          <t>Client</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>AWS object storage service used to store multimedia files.</t>
+          <t>The client is the user of the platform, who performs the different requests.</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>['AU_05']</t>
-        </is>
-      </c>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>AU_12</t>
+          <t>AU_01</t>
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Amazon S3</t>
+          <t>Client</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>This is AWS's object storage service.</t>
+          <t>On one side is the client, who makes the various requests, and on the other side is the server, who receives and processes them.</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>CF_M09_AU39</t>
+          <t>CF_M09_P01</t>
         </is>
       </c>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
         <is>
-          <t>CF_M09_AU25</t>
+          <t>CF_M09_AU06</t>
         </is>
       </c>
       <c r="T15" t="inlineStr"/>
@@ -2305,17 +2293,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>P_03</t>
+          <t>AU_12</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CF_M09_P03</t>
+          <t>CF_M09_AU25</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>pattern</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -2323,63 +2311,63 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Flux</t>
+          <t>Amazon S3</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Design Pattern</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Flux is a frontend architecture based on the Model-View-Controller (MVC) design pattern, but with the difference that there is no bidirectional communication between the view and the model.</t>
+          <t>AWS object storage service used to store multimedia files.</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>58</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>['AU_03']</t>
+          <t>['AU_05']</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>P_03</t>
+          <t>AU_12</t>
         </is>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Flux</t>
+          <t>Amazon S3</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Architectural Pattern</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>A logical architecture called Flux has been used for the development of the presentation layer.</t>
+          <t>This is AWS's object storage service.</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>CF_M09_AU34</t>
+          <t>CF_M09_AU39</t>
         </is>
       </c>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr">
         <is>
-          <t>CF_M09_P03</t>
+          <t>CF_M09_AU25</t>
         </is>
       </c>
       <c r="T16" t="inlineStr"/>
@@ -2387,17 +2375,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AU_10</t>
+          <t>P_03</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CF_M09_AU03</t>
+          <t>CF_M09_P03</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>pattern</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -2405,55 +2393,59 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS</t>
+          <t>Flux</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Architectural Pattern</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cloud computing services used for infrastructure.</t>
+          <t>Flux is an architecture for frontend development based on unidirectional data flow.</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>56</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>AU_10</t>
+          <t>P_03</t>
         </is>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>AWS</t>
+          <t>Flux</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Architectural Pattern</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Within the software engineering specialization, this project focuses on web technologies, specifically using React [2] and Nest [3] for the codebase and AWS cloud services [4] for the infrastructure.</t>
+          <t>A logical architecture called Flux has been used for the development of the presentation layer.</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q17" t="inlineStr"/>
+        <v>56</v>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>CF_M09_AU34</t>
+        </is>
+      </c>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr">
         <is>
-          <t>CF_M09_AU03</t>
+          <t>CF_M09_P03</t>
         </is>
       </c>
       <c r="T17" t="inlineStr"/>
@@ -2461,17 +2453,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P_02</t>
+          <t>AU_10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CF_M09_P02</t>
+          <t>CF_M09_AU03</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>pattern</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -2479,55 +2471,55 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Three Layers</t>
+          <t>AWS</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Architectural Pattern</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>This architecture divides the system into three parts, the presentation layer, the business layer and the data layer.</t>
+          <t>Cloud computing services used for infrastructure.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>61</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>P_02</t>
+          <t>AU_10</t>
         </is>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Three Layers</t>
+          <t>AWS</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Architectural Pattern</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>To decouple the components of the client-server model, a three-tier architecture has been used.</t>
+          <t>Within the software engineering specialization, this project focuses on web technologies, specifically using React [2] and Nest [3] for the codebase and AWS cloud services [4] for the infrastructure.</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>55</v>
+        <v>9</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr">
         <is>
-          <t>CF_M09_P02</t>
+          <t>CF_M09_AU03</t>
         </is>
       </c>
       <c r="T18" t="inlineStr"/>
@@ -2535,17 +2527,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AU_13</t>
+          <t>P_02</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CF_M09_AU27</t>
+          <t>CF_M09_P02</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>pattern</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -2553,63 +2545,59 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Amazon DynamoDB</t>
+          <t>Three Layers</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Architectural Pattern</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>AWS service used for user cache.</t>
+          <t>This architecture divides the system into three parts: the presentation layer, the business layer, and the data layer.</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>55</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>['AU_05']</t>
+          <t>['P_01']</t>
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>AU_13</t>
+          <t>P_02</t>
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Amazon DynamoDB</t>
+          <t>Three Layers</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Architectural Pattern</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>To improve system response speed, there is a user cache system stored in Amazon DynamoDB</t>
+          <t>To decouple the components of the client-server model, a three-tier architecture has been used.</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>58</v>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>CF_M09_AU10</t>
-        </is>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr">
         <is>
-          <t>CF_M09_AU27</t>
+          <t>CF_M09_P02</t>
         </is>
       </c>
       <c r="T19" t="inlineStr"/>
@@ -2617,12 +2605,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AU_20</t>
+          <t>AU_13</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CF_M09_AU21</t>
+          <t>CF_M09_AU27</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2635,7 +2623,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>TCP</t>
+          <t>Amazon DynamoDB</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2645,39 +2633,39 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>La comunicaci´ on se realiza mediante el protocolo de comunicaci´ on TCP.</t>
+          <t>AWS NoSQL database service used for user cache.</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>58</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>['AU_15']</t>
+          <t>['AU_05']</t>
         </is>
       </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
-          <t>AU_20</t>
+          <t>AU_13</t>
         </is>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>TCP</t>
+          <t>Amazon DynamoDB</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Communication is carried out using the TCP communication protocol</t>
+          <t>To improve system response speed, there is a user cache system stored in Amazon DynamoDB</t>
         </is>
       </c>
       <c r="P20" t="n">
@@ -2685,16 +2673,98 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>CF_M09_AU20</t>
+          <t>CF_M09_AU10</t>
         </is>
       </c>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr">
         <is>
+          <t>CF_M09_AU27</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>AU_15</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
           <t>CF_M09_AU21</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>TCP</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Communication protocol used between business and functional services.</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>['AU_17']</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>AU_15</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>TCP</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Communication is carried out using the TCP communication protocol</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>CF_M09_AU20</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>CF_M09_AU21</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2707,7 +2777,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2838,32 +2908,32 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>functional service, data layer</t>
+          <t>presentation layer, business layer</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Es el servicio que tiene comunicaci´ on con la capa de datos.</t>
+          <t>La comunicaci´ on entre ambos se realiza a trav´ es de internet utilizando el modelo de REST API [...] y el protocolo de comunicaci´ on HTTP.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CF_M09_AU10</t>
+          <t>CF_M09_AU40</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Data layer</t>
+          <t>HTTP</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.7706</v>
+        <v>0.7917</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AU_17</t>
+          <t>AU_18</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2874,26 +2944,26 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>business service, amazon dynamodb</t>
+          <t>functional service, data layer</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Cache de usuarios: Para mejorar la velocidad de respuesta del sistema, existe un sistema de cach´ e de usuarios almacenada en Amazon DynamoDB, a la cu´ al tiene acceso el servicio business.</t>
+          <t>Es el servicio que tiene comunicaci´ on con la capa de datos.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CF_M09_AU26</t>
+          <t>CF_M09_AU10</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>User Cache</t>
+          <t>Data layer</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.7848000000000001</v>
+        <v>0.7706</v>
       </c>
     </row>
     <row r="6">
@@ -2904,28 +2974,68 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>HTTP</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>business service, amazon dynamodb</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>La comunicaci´ on entre ambos se realiza a trav´ es de internet utilizando el modelo de REST API y el protocolo de comunicaci´ on HTTP.</t>
+          <t>Cache de usuarios [...] a la cu´ al tiene acceso el servicio business.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CF_M09_AU38</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
+          <t>CF_M09_AU26</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>User Cache</t>
+        </is>
+      </c>
       <c r="H6" t="n">
-        <v>0.7066</v>
+        <v>0.8102</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>P_06</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Design Pattern</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>This pattern allows encapsulating information and exposing only that which is desired to be shared between modules.</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>CF_M09_AU35</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Modules</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>0.9649</v>
       </c>
     </row>
   </sheetData>
@@ -3008,16 +3118,16 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>P_04</t>
+          <t>P_05</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Observer</t>
+          <t>Provider</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.6791</v>
+        <v>0.6886</v>
       </c>
     </row>
     <row r="3">
@@ -3059,43 +3169,43 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CF_M09_AU11</t>
+          <t>CF_M09_AU07</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Component</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>client, waapiti platform</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>This is the part responsible for displaying information to the user.</t>
+          <t>On one side is the client, who makes the various requests, and on the other side is the server, who receives and processes them.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>P_04</t>
+          <t>P_01</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Observer</t>
+          <t>Client-Server</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.7618</v>
+        <v>0.8557</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CF_M09_AU12</t>
+          <t>CF_M09_AU11</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3105,33 +3215,33 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Actions</t>
+          <t>View</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>These are the actions that the user can perform.</t>
+          <t>This is the part responsible for displaying information to the user.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>AU_08</t>
+          <t>P_04</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>React</t>
+          <t>Observer</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.7452</v>
+        <v>0.7618</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CF_M09_AU13</t>
+          <t>CF_M09_AU12</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -3141,33 +3251,33 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dispatcher</t>
+          <t>Actions</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> It is responsible for receiving the actions and sending them to the store to modify its state.</t>
+          <t>These are the actions that the user can perform.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>AU_02</t>
+          <t>AU_08</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Server</t>
+          <t>React</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.6807</v>
+        <v>0.7452</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CF_M09_AU14</t>
+          <t>CF_M09_AU13</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3177,69 +3287,69 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Dispatcher</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>It is responsible for storing the application state.</t>
+          <t xml:space="preserve"> It is responsible for receiving the actions and sending them to the store to modify its state.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AU_06</t>
+          <t>P_05</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Business Service</t>
+          <t>Provider</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.6739000000000001</v>
+        <v>0.7081</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CF_M09_AU15</t>
+          <t>CF_M09_AU14</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>actions, store</t>
-        </is>
-      </c>
+          <t>Component</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Store</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>They are defined as JavaScript objects and indicate the intention to modify the application's state.</t>
+          <t>It is responsible for storing the application state.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AU_09</t>
+          <t>P_05</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>NestJS</t>
+          <t>Provider</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0.6073</v>
+        <v>0.6902</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CF_M09_AU16</t>
+          <t>CF_M09_AU15</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3250,240 +3360,240 @@
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>dispatcher, store</t>
+          <t>actions, store</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>It is responsible for receiving the actions and sending them to the store to modify its state.</t>
+          <t>They are defined as JavaScript objects and indicate the intention to modify the application's state.</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>AU_16</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr"/>
+          <t>P_06</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
       <c r="H9" t="n">
-        <v>0.6985</v>
+        <v>0.6199</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CF_M09_AU17</t>
+          <t>CF_M09_AU16</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Redux</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>dispatcher, store</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Redux is a JavaScript library that allows you to implement the Flux architecture.</t>
+          <t>It is responsible for receiving the actions and sending them to the store to modify its state.</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>AU_08</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>React</t>
-        </is>
-      </c>
+          <t>AU_18</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
-        <v>0.7194</v>
+        <v>0.6985</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CF_M09_AU18</t>
+          <t>CF_M09_AU17</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Layer</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Presentation layer (Backend)</t>
+          <t>Redux</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>In this case, the presentation layer is not complex. It corresponds to the user's web browser.</t>
+          <t>Redux is a JavaScript library that allows you to implement the Flux architecture.</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>AU_03</t>
+          <t>AU_08</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Presentation Layer</t>
+          <t>React</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0.9188</v>
+        <v>0.7194</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CF_M09_AU23</t>
+          <t>CF_M09_AU18</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Layer</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>RDS</t>
+          <t>Presentation layer (Backend)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RDS is a distributed relational database service. In the case of Waapiti, a MySQL database is used and contains all the system information.</t>
+          <t>In this case, the presentation layer is not complex. It corresponds to the user's web browser.</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>AU_18</t>
+          <t>AU_03</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>REST</t>
+          <t>Presentation Layer</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>0.6775</v>
+        <v>0.9188</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CF_M09_AU26</t>
+          <t>CF_M09_AU22</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Component</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>User Cache</t>
+          <t>REST</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>To improve system response speed, there is a user cache system stored in Amazon DynamoDB</t>
+          <t>Defines REST API routes and processes requests to send them to the functional service.</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>AU_17</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr"/>
+          <t>AU_14</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
       <c r="H13" t="n">
-        <v>0.7848000000000001</v>
+        <v>0.6758999999999999</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CF_M09_AU28</t>
+          <t>CF_M09_AU23</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Typescript</t>
+          <t>RDS</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>is a superset of JavaScript. It has been used to develop both the backend.</t>
+          <t>RDS is a distributed relational database service. In the case of Waapiti, a MySQL database is used and contains all the system information.</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>AU_09</t>
+          <t>P_05</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>NestJS</t>
+          <t>Provider</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>0.697</v>
+        <v>0.6294999999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CF_M09_AU29</t>
+          <t>CF_M09_AU26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Component</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>TypeORM</t>
+          <t>User Cache</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>is an ORM (Object Relational Mapping) [41] for TypeScript and JavaScript.</t>
+          <t>To improve system response speed, there is a user cache system stored in Amazon DynamoDB</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>AU_11</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>MySQL</t>
-        </is>
-      </c>
+          <t>AU_19</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>0.6622</v>
+        <v>0.8102</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CF_M09_AU30</t>
+          <t>CF_M09_AU28</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3493,33 +3603,33 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Material UI</t>
+          <t>Typescript</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>is a React library that contains user interface components.</t>
+          <t>is a superset of JavaScript. It has been used to develop both the backend.</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>AU_03</t>
+          <t>AU_09</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Presentation Layer</t>
+          <t>NestJS</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>0.6683</v>
+        <v>0.697</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CF_M09_AU31</t>
+          <t>CF_M09_AU29</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3529,33 +3639,33 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>NextJS</t>
+          <t>TypeORM</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>is a React meta-framework that allows you to easily create web applications (since it provides utilities such as web routing).</t>
+          <t>is an ORM (Object Relational Mapping) [41] for TypeScript and JavaScript.</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>AU_09</t>
+          <t>AU_11</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>NestJS</t>
+          <t>MySQL</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>0.7692</v>
+        <v>0.6622</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CF_M09_AU32</t>
+          <t>CF_M09_AU30</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3565,121 +3675,121 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Shadcn</t>
+          <t>Material UI</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>is a reusable UI component project that features a modern design and focuses on accessibility and ease of customization of components.</t>
+          <t>is a React library that contains user interface components.</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>AU_20</t>
+          <t>AU_03</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>TCP</t>
+          <t>Presentation Layer</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>0.6069</v>
+        <v>0.6683</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CF_M09_AU33</t>
+          <t>CF_M09_AU31</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>NextJS</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>It should be clear that in this project the author has worked on the entire system, both backend and frontend.</t>
+          <t>is a React meta-framework that allows you to easily create web applications (since it provides utilities such as web routing).</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>AU_04</t>
+          <t>AU_09</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Business Layer</t>
+          <t>NestJS</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>0.706</v>
+        <v>0.7692</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CF_M09_AU34</t>
+          <t>CF_M09_AU32</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Frontend</t>
+          <t>Shadcn</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>It should be clear that in this project the author has worked on the entire system, both backend and frontend.</t>
+          <t>is a reusable UI component project that features a modern design and focuses on accessibility and ease of customization of components.</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>AU_03</t>
+          <t>P_05</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Presentation Layer</t>
+          <t>Provider</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>0.7635</v>
+        <v>0.6219</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CF_M09_AU35</t>
+          <t>CF_M09_AU33</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Component</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Modules</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Modules are classes that allow NestJS to organize the application.</t>
+          <t>It should be clear that in this project the author has worked on the entire system, both backend and frontend.</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -3693,49 +3803,49 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>0.6216</v>
+        <v>0.706</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CF_M09_AU36</t>
+          <t>CF_M09_AU34</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Component</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Controllers</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Controllers are responsible for receiving and processing HTTP requests.</t>
+          <t>It should be clear that in this project the author has worked on the entire system, both backend and frontend.</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>P_01</t>
+          <t>AU_03</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Client-Server</t>
+          <t>Presentation Layer</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>0.6403</v>
+        <v>0.7635</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CF_M09_AU37</t>
+          <t>CF_M09_AU35</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3745,173 +3855,173 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Providers</t>
+          <t>Modules</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Providers are classes that can act as services, repositories, factories, helpers, etc.</t>
+          <t>Modules are classes that allow NestJS to organize the application.</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>AU_06</t>
+          <t>P_06</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Business Service</t>
+          <t>Module</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>0.711</v>
+        <v>0.9649</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CF_M09_AU38</t>
+          <t>CF_M09_AU36</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>client, business layer (backend)</t>
-        </is>
-      </c>
+          <t>Component</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Controllers</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Therefore, controllers are responsible for receiving HTTP requests and forwarding them to the providers.</t>
+          <t>Controllers are responsible for receiving and processing HTTP requests.</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>AU_14</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr"/>
+          <t>P_05</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Provider</t>
+        </is>
+      </c>
       <c r="H24" t="n">
-        <v>0.7108</v>
+        <v>0.6703</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CF_M09_AU39</t>
+          <t>CF_M09_AU37</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Layer</t>
+          <t>Component</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Data Layer (Backend)</t>
+          <t>Providers</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>The data layer is divided into several AWS services that allow for improved system performance and scalability.</t>
+          <t>Providers are classes that can act as services, repositories, factories, helpers, etc.</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>AU_05</t>
+          <t>P_05</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Data Layer</t>
+          <t>Provider</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>0.9248</v>
+        <v>0.9526</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CF_M09_P05</t>
+          <t>CF_M09_AU38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Design Pattern</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Provider pattern</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>client, business layer (backend)</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>The provider pattern is a software design pattern that allows sharing information between React components without the need to use props.</t>
+          <t>Therefore, controllers are responsible for receiving HTTP requests and forwarding them to the providers.</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>AU_07</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Functional Service</t>
-        </is>
-      </c>
+          <t>AU_17</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
-        <v>0.717</v>
+        <v>0.707</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CF_M09_P06</t>
+          <t>CF_M09_AU39</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Design Pattern</t>
+          <t>Layer</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Module Pattern</t>
+          <t>Data Layer (Backend)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>This is the most important pattern in the JavaScript language.</t>
+          <t>The data layer is divided into several AWS services that allow for improved system performance and scalability.</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>AU_04</t>
+          <t>AU_05</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Business Layer</t>
+          <t>Data Layer</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>0.6344</v>
+        <v>0.9248</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CF_M09_P07</t>
+          <t>CF_M09_P06</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3921,27 +4031,27 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Hook pattern</t>
+          <t>Module Pattern</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Hooks are a new feature in React that allows you to use state and other React features without writing a class.</t>
+          <t>This is the most important pattern in the JavaScript language.</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>AU_19</t>
+          <t>P_06</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>HTTP</t>
+          <t>Module</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>0.6038</v>
+        <v>0.9157999999999999</v>
       </c>
     </row>
     <row r="29">

--- a/outputs/evaluation/architecture/validation/CF_M09/run_3/CF_M09_arch_eval.xlsx
+++ b/outputs/evaluation/architecture/validation/CF_M09/run_3/CF_M09_arch_eval.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -440,6 +440,11 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>f1</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>mean semantic meaning</t>
         </is>
       </c>
@@ -456,7 +461,10 @@
       <c r="C2" t="n">
         <v>0.4167</v>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" t="n">
+        <v>0.5405</v>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -475,6 +483,9 @@
         <v>0.4419</v>
       </c>
       <c r="D3" t="n">
+        <v>0.5846</v>
+      </c>
+      <c r="E3" t="n">
         <v>0.9578</v>
       </c>
     </row>
@@ -491,6 +502,9 @@
         <v>0.2</v>
       </c>
       <c r="D4" t="n">
+        <v>0.2222</v>
+      </c>
+      <c r="E4" t="n">
         <v>0.7516</v>
       </c>
     </row>
@@ -1201,7 +1215,6 @@
       <c r="D2" t="n">
         <v>0.7516</v>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1222,7 +1235,6 @@
           <t>['AU_06', 'AU_07']</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>AU_17</t>
@@ -1233,7 +1245,6 @@
           <t>business service, functional service</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1252,7 +1263,6 @@
           <t>CF_M09_AU06, CF_M09_AU19</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
           <t>CF_M09_AU20</t>
@@ -1308,13 +1318,11 @@
           <t>['AU_04']</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>AU_06</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>Business layer</t>
@@ -1338,13 +1346,11 @@
           <t>CF_M09_P02</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
           <t>CF_M09_AU09</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1385,14 +1391,11 @@
           <t>59</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>P_04</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>Observer pattern</t>
@@ -1416,13 +1419,11 @@
           <t>CF_M09_P03</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
           <t>CF_M09_P04</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1463,14 +1464,11 @@
           <t>59</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>P_05</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
           <t>Provider pattern</t>
@@ -1494,13 +1492,11 @@
           <t>CF_M09_AU01</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
           <t>CF_M09_P05</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1541,14 +1537,11 @@
           <t>59</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>P_07</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
           <t>Hook pattern</t>
@@ -1572,13 +1565,11 @@
           <t>CF_M09_AU01</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
           <t>CF_M09_P07</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1619,14 +1610,11 @@
           <t>55</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>P_01</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
           <t>Client-Server Architecture</t>
@@ -1645,14 +1633,11 @@
       <c r="P7" t="n">
         <v>55</v>
       </c>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
           <t>CF_M09_P01</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1693,14 +1678,11 @@
           <t>55</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>AU_04</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>Business layer (Backend)</t>
@@ -1724,13 +1706,11 @@
           <t>CF_M09_P02</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
           <t>CF_M09_AU19</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1771,14 +1751,11 @@
           <t>55</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>AU_03</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
           <t>Presentation layer</t>
@@ -1802,13 +1779,11 @@
           <t>CF_M09_P02</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
           <t>CF_M09_AU08</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1849,14 +1824,11 @@
           <t>55</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>AU_05</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
           <t>Data layer</t>
@@ -1880,13 +1852,11 @@
           <t>CF_M09_P02</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
           <t>CF_M09_AU10</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1932,13 +1902,11 @@
           <t>['AU_03']</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>AU_08</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
           <t>React</t>
@@ -1962,13 +1930,11 @@
           <t>CF_M09_AU34</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
           <t>CF_M09_AU01</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2014,13 +1980,11 @@
           <t>['AU_05']</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>AU_11</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
           <t>MySQL</t>
@@ -2044,13 +2008,11 @@
           <t>CF_M09_AU23</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
           <t>CF_M09_AU24</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2096,13 +2058,11 @@
           <t>['AU_16']</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>AU_14</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
           <t>HTTP</t>
@@ -2121,14 +2081,11 @@
       <c r="P13" t="n">
         <v>55</v>
       </c>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
           <t>CF_M09_AU40</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2174,13 +2131,11 @@
           <t>['AU_06', 'AU_07']</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>AU_09</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
           <t>NestJS</t>
@@ -2204,13 +2159,11 @@
           <t>CF_M09_AU33</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
           <t>CF_M09_AU02</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2251,14 +2204,11 @@
           <t>55</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
           <t>AU_01</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
           <t>Client</t>
@@ -2282,13 +2232,11 @@
           <t>CF_M09_P01</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
         <is>
           <t>CF_M09_AU06</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2334,13 +2282,11 @@
           <t>['AU_05']</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
           <t>AU_12</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
           <t>Amazon S3</t>
@@ -2364,13 +2310,11 @@
           <t>CF_M09_AU39</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr">
         <is>
           <t>CF_M09_AU25</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2411,14 +2355,11 @@
           <t>56</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
           <t>P_03</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
           <t>Flux</t>
@@ -2442,13 +2383,11 @@
           <t>CF_M09_AU34</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr">
         <is>
           <t>CF_M09_P03</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2489,14 +2428,11 @@
           <t>61</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
           <t>AU_10</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
           <t>AWS</t>
@@ -2515,14 +2451,11 @@
       <c r="P18" t="n">
         <v>9</v>
       </c>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr">
         <is>
           <t>CF_M09_AU03</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2568,13 +2501,11 @@
           <t>['P_01']</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
           <t>P_02</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
           <t>Three Layers</t>
@@ -2593,14 +2524,11 @@
       <c r="P19" t="n">
         <v>55</v>
       </c>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr">
         <is>
           <t>CF_M09_P02</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2646,13 +2574,11 @@
           <t>['AU_05']</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
           <t>AU_13</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
           <t>Amazon DynamoDB</t>
@@ -2676,13 +2602,11 @@
           <t>CF_M09_AU10</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr">
         <is>
           <t>CF_M09_AU27</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2728,13 +2652,11 @@
           <t>['AU_17']</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
           <t>AU_15</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
           <t>TCP</t>
@@ -2758,13 +2680,11 @@
           <t>CF_M09_AU20</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr">
         <is>
           <t>CF_M09_AU21</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2838,7 +2758,6 @@
           <t>Server</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>The server is the software that is responsible for processing user requests.</t>
@@ -2874,7 +2793,6 @@
           <t>Functional Service</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>Service that performs all the important logic of the platform and communicates with the data layer.</t>
@@ -2905,7 +2823,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>presentation layer, business layer</t>
@@ -2941,7 +2858,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>functional service, data layer</t>
@@ -2977,7 +2893,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>business service, amazon dynamodb</t>
@@ -3018,7 +2933,6 @@
           <t>Module</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>This pattern allows encapsulating information and exposing only that which is desired to be shared between modules.</t>
@@ -3110,7 +3024,6 @@
           <t>Player</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>A player is an external device that allows content to be played on a non professional screen.</t>
@@ -3146,7 +3059,6 @@
           <t>Waapiti Platform</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>The main objective of this work is the development of an asset management module that expands the Waapiti software platform and allows us to solve a series of problems and needs of the company.</t>
@@ -3177,7 +3089,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>client, waapiti platform</t>
@@ -3218,7 +3129,6 @@
           <t>View</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>This is the part responsible for displaying information to the user.</t>
@@ -3254,7 +3164,6 @@
           <t>Actions</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>These are the actions that the user can perform.</t>
@@ -3290,7 +3199,6 @@
           <t>Dispatcher</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t xml:space="preserve"> It is responsible for receiving the actions and sending them to the store to modify its state.</t>
@@ -3326,7 +3234,6 @@
           <t>Store</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>It is responsible for storing the application state.</t>
@@ -3357,7 +3264,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
           <t>actions, store</t>
@@ -3393,7 +3299,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
           <t>dispatcher, store</t>
@@ -3409,7 +3314,6 @@
           <t>AU_18</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
         <v>0.6985</v>
       </c>
@@ -3430,7 +3334,6 @@
           <t>Redux</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>Redux is a JavaScript library that allows you to implement the Flux architecture.</t>
@@ -3466,7 +3369,6 @@
           <t>Presentation layer (Backend)</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>In this case, the presentation layer is not complex. It corresponds to the user's web browser.</t>
@@ -3502,7 +3404,6 @@
           <t>REST</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>Defines REST API routes and processes requests to send them to the functional service.</t>
@@ -3538,7 +3439,6 @@
           <t>RDS</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>RDS is a distributed relational database service. In the case of Waapiti, a MySQL database is used and contains all the system information.</t>
@@ -3574,7 +3474,6 @@
           <t>User Cache</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>To improve system response speed, there is a user cache system stored in Amazon DynamoDB</t>
@@ -3585,7 +3484,6 @@
           <t>AU_19</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
         <v>0.8102</v>
       </c>
@@ -3606,7 +3504,6 @@
           <t>Typescript</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
           <t>is a superset of JavaScript. It has been used to develop both the backend.</t>
@@ -3642,7 +3539,6 @@
           <t>TypeORM</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>is an ORM (Object Relational Mapping) [41] for TypeScript and JavaScript.</t>
@@ -3678,7 +3574,6 @@
           <t>Material UI</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>is a React library that contains user interface components.</t>
@@ -3714,7 +3609,6 @@
           <t>NextJS</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
           <t>is a React meta-framework that allows you to easily create web applications (since it provides utilities such as web routing).</t>
@@ -3750,7 +3644,6 @@
           <t>Shadcn</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
           <t>is a reusable UI component project that features a modern design and focuses on accessibility and ease of customization of components.</t>
@@ -3786,7 +3679,6 @@
           <t>Backend</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
           <t>It should be clear that in this project the author has worked on the entire system, both backend and frontend.</t>
@@ -3822,7 +3714,6 @@
           <t>Frontend</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
           <t>It should be clear that in this project the author has worked on the entire system, both backend and frontend.</t>
@@ -3858,7 +3749,6 @@
           <t>Modules</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
           <t>Modules are classes that allow NestJS to organize the application.</t>
@@ -3894,7 +3784,6 @@
           <t>Controllers</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
           <t>Controllers are responsible for receiving and processing HTTP requests.</t>
@@ -3930,7 +3819,6 @@
           <t>Providers</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
           <t>Providers are classes that can act as services, repositories, factories, helpers, etc.</t>
@@ -3961,7 +3849,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
           <t>client, business layer (backend)</t>
@@ -3977,7 +3864,6 @@
           <t>AU_17</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
         <v>0.707</v>
       </c>
@@ -3998,7 +3884,6 @@
           <t>Data Layer (Backend)</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
           <t>The data layer is divided into several AWS services that allow for improved system performance and scalability.</t>
@@ -4034,7 +3919,6 @@
           <t>Module Pattern</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
           <t>This is the most important pattern in the JavaScript language.</t>
@@ -4070,7 +3954,6 @@
           <t>ORM</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
           <t>TypeORM is an ORM (Object Relational Mapping) that allows you to define database entities as TypeScript classes.</t>
